--- a/MoneyKeel/documents/audit/moneykeel_audit_assessment_module-readiness_v01.xlsx
+++ b/MoneyKeel/documents/audit/moneykeel_audit_assessment_module-readiness_v01.xlsx
@@ -826,17 +826,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>APPROVED (mocks), NOT TRACED (which build shipped them)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>No approved design on file. Two word collisions found on 2026-09-14 are still open ("Add by hand" adds an EXPENSE here; "Disconnect").</t>
+          <t>CORRECTED 2026-09-26. Four approved mocks are filed in MoneyKeel/documents/cashflow: income end to end v07 (v4, v5 and v6 each approved in the changelog — v6 on 2026-09-02, "Mock v6 approved and live"; v07 is that mock with the canon words applied on 2026-09-12), This month + Spending v06 (2026-08-26), Look ahead v03, and the four-tab surface v01. My first pass said "NOT RECORDED" because it read only the design-each-screen-was-built-from record, which carries three screens and says Cash flow was never TRACED — a different thing from never approved.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Trace which build shipped which mock, by the fingerprint method, and record it. Settle whether income v07 supersedes v06 (its file says v07, its eyebrow still says v6). The two word collisions stay open.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
